--- a/sources/julia_step6.xlsx
+++ b/sources/julia_step6.xlsx
@@ -863,6 +863,11 @@
           <t>Special Tag Throw with Michelle only. Michelle finishes with a Lariat. Total damage is 12,24.</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>1b569aeb-dd63-4db9-bfe2-caa3a868a11d</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>1b569aeb-dd63-4db9-bfe2-caa3a868a11d</t>
@@ -910,6 +915,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>48718773-f00b-471d-8dc4-830794a42ebc</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>48718773-f00b-471d-8dc4-830794a42ebc</t>
@@ -957,6 +967,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>35dc67c0-d4fa-495c-aefc-39f34e65507b</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>35dc67c0-d4fa-495c-aefc-39f34e65507b</t>
@@ -1002,6 +1017,11 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>b70b8f8a-633b-40a2-8811-5f4191813631</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -5912,6 +5932,11 @@
           <t>hmmhLmhhLm</t>
         </is>
       </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>f26af970-57e3-45d4-baba-6711c2809508</t>
+        </is>
+      </c>
       <c r="Q103" t="inlineStr">
         <is>
           <t>f26af970-57e3-45d4-baba-6711c2809508</t>
@@ -5944,6 +5969,11 @@
           <t>hmmhLmmLm!</t>
         </is>
       </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>8ba99c8f-7b6d-46d5-860f-492405778df4</t>
+        </is>
+      </c>
       <c r="Q104" t="inlineStr">
         <is>
           <t>8ba99c8f-7b6d-46d5-860f-492405778df4</t>
@@ -5974,6 +6004,11 @@
       <c r="K105" t="inlineStr">
         <is>
           <t>hmmhLmmmLm</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>12d35c24-0209-43bc-a4fa-a6173fd493c0</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">

--- a/sources/julia_step6.xlsx
+++ b/sources/julia_step6.xlsx
@@ -4133,6 +4133,11 @@
           <t>– 1+2</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="C70" t="inlineStr">
         <is>
           <t>– Back Push</t>
